--- a/Analysed/Gemini_gemini-3-flash-preview_cot.xlsx
+++ b/Analysed/Gemini_gemini-3-flash-preview_cot.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H3" t="n">
-        <v>1.698479532163743</v>
+        <v>1.71728323699422</v>
       </c>
       <c r="I3" t="n">
-        <v>1.954260527802349</v>
+        <v>1.97554909320249</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02352941176470588</v>
+        <v>0.02325581395348837</v>
       </c>
     </row>
     <row r="4">
@@ -649,10 +649,10 @@
         <v>50</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1654</v>
+        <v>3.1674</v>
       </c>
       <c r="I5" t="n">
-        <v>3.424418490780588</v>
+        <v>3.427255753514756</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5774666666666666</v>
+        <v>0.5627272727272726</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7999808331037273</v>
+        <v>0.7895247625308219</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3648648648648649</v>
+        <v>0.3815789473684211</v>
       </c>
     </row>
     <row r="11">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5080701754385966</v>
+        <v>0.5044067796610169</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5975828504549765</v>
+        <v>0.59196598619647</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4464285714285715</v>
+        <v>0.4655172413793103</v>
       </c>
     </row>
     <row r="12">
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H13" t="n">
-        <v>6.207021943573667</v>
+        <v>6.268074534161491</v>
       </c>
       <c r="I13" t="n">
-        <v>7.220301837228805</v>
+        <v>7.291364713061745</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9528301886792453</v>
+        <v>0.9439252336448598</v>
       </c>
     </row>
     <row r="14">
@@ -1174,16 +1174,16 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H17" t="n">
-        <v>1.255294117647059</v>
+        <v>1.273846153846154</v>
       </c>
       <c r="I17" t="n">
-        <v>1.555750874759107</v>
+        <v>1.571175454140087</v>
       </c>
       <c r="J17" t="n">
-        <v>0.78</v>
+        <v>0.7647058823529411</v>
       </c>
     </row>
     <row r="18">
@@ -1218,16 +1218,16 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H18" t="n">
-        <v>1.577297297297297</v>
+        <v>1.606052631578948</v>
       </c>
       <c r="I18" t="n">
-        <v>1.958377706992</v>
+        <v>1.980383402539172</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.4864864864864865</v>
       </c>
     </row>
     <row r="19">
@@ -1526,16 +1526,16 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H25" t="n">
-        <v>13.92754098360656</v>
+        <v>13.60048</v>
       </c>
       <c r="I25" t="n">
-        <v>15.58332768183177</v>
+        <v>15.39528301785972</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3548387096774194</v>
       </c>
     </row>
     <row r="26">
@@ -1658,16 +1658,16 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H28" t="n">
-        <v>11.40391304347826</v>
+        <v>11.22723404255319</v>
       </c>
       <c r="I28" t="n">
-        <v>13.22358844279221</v>
+        <v>13.08996806068629</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.5869565217391305</v>
       </c>
     </row>
     <row r="29">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H31" t="n">
-        <v>20.24169491525424</v>
+        <v>20.00512396694215</v>
       </c>
       <c r="I31" t="n">
-        <v>20.88722937221348</v>
+        <v>20.69538204567698</v>
       </c>
       <c r="J31" t="n">
-        <v>0.811965811965812</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="32">
@@ -1834,16 +1834,16 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H32" t="n">
-        <v>15.48030303030303</v>
+        <v>15.62428571428571</v>
       </c>
       <c r="I32" t="n">
-        <v>15.58109479951634</v>
+        <v>15.72934200785271</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2753623188405797</v>
       </c>
     </row>
     <row r="33">
@@ -2010,16 +2010,16 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H36" t="n">
-        <v>12.01052631578948</v>
+        <v>10.340625</v>
       </c>
       <c r="I36" t="n">
-        <v>12.09410469696094</v>
+        <v>10.65937087730791</v>
       </c>
       <c r="J36" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1935483870967742</v>
       </c>
     </row>
     <row r="37">
@@ -2142,16 +2142,16 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H39" t="n">
-        <v>21.63037037037037</v>
+        <v>21.65927272727273</v>
       </c>
       <c r="I39" t="n">
-        <v>25.7529901176543</v>
+        <v>25.70917749117476</v>
       </c>
       <c r="J39" t="n">
-        <v>0.08411214953271028</v>
+        <v>0.08256880733944955</v>
       </c>
     </row>
     <row r="40">
@@ -2186,16 +2186,16 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H40" t="n">
-        <v>26.45705128205128</v>
+        <v>25.920625</v>
       </c>
       <c r="I40" t="n">
-        <v>29.08254179365152</v>
+        <v>28.73824879407233</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1558441558441558</v>
+        <v>0.1518987341772152</v>
       </c>
     </row>
     <row r="41">
@@ -2230,16 +2230,16 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H41" t="n">
-        <v>25.06279069767442</v>
+        <v>26.40666666666666</v>
       </c>
       <c r="I41" t="n">
-        <v>32.58600855410757</v>
+        <v>33.92005044545515</v>
       </c>
       <c r="J41" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="42">
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H42" t="n">
-        <v>15.22071428571428</v>
+        <v>15.22852941176471</v>
       </c>
       <c r="I42" t="n">
-        <v>16.4626141388819</v>
+        <v>16.28239729783996</v>
       </c>
       <c r="J42" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.2424242424242424</v>
       </c>
     </row>
     <row r="43">
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H43" t="n">
-        <v>21.75314814814814</v>
+        <v>21.73107692307692</v>
       </c>
       <c r="I43" t="n">
-        <v>22.24099684683087</v>
+        <v>22.2214757662665</v>
       </c>
       <c r="J43" t="n">
-        <v>0.07739938080495357</v>
+        <v>0.08024691358024691</v>
       </c>
     </row>
     <row r="44">
@@ -2358,20 +2358,20 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>115</v>
+        <v>206</v>
       </c>
       <c r="H44" t="n">
-        <v>17.99826086956522</v>
+        <v>21.4118932038835</v>
       </c>
       <c r="I44" t="n">
-        <v>18.7063453080127</v>
+        <v>21.94256475570376</v>
       </c>
       <c r="J44" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1317073170731707</v>
       </c>
     </row>
     <row r="45">
@@ -2402,20 +2402,20 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="H45" t="n">
-        <v>31.52294117647059</v>
+        <v>17.99826086956522</v>
       </c>
       <c r="I45" t="n">
-        <v>33.36867335056146</v>
+        <v>18.7063453080127</v>
       </c>
       <c r="J45" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2105263157894737</v>
       </c>
     </row>
     <row r="46">
@@ -2446,20 +2446,20 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="H46" t="n">
-        <v>15.38035714285714</v>
+        <v>31.52294117647059</v>
       </c>
       <c r="I46" t="n">
-        <v>17.7342222633448</v>
+        <v>33.36867335056146</v>
       </c>
       <c r="J46" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="47">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="H47" t="n">
-        <v>28.49285714285714</v>
+        <v>15.38035714285714</v>
       </c>
       <c r="I47" t="n">
-        <v>32.5917626899512</v>
+        <v>17.7342222633448</v>
       </c>
       <c r="J47" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="48">
@@ -2529,25 +2529,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OPENING</t>
+          <t>OPENING-CLOSING</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>315</v>
+        <v>42</v>
       </c>
       <c r="H48" t="n">
-        <v>29.49647619047619</v>
+        <v>28.49285714285714</v>
       </c>
       <c r="I48" t="n">
-        <v>30.87753749228234</v>
+        <v>32.5917626899512</v>
       </c>
       <c r="J48" t="n">
-        <v>0.06687898089171974</v>
+        <v>0.3658536585365854</v>
       </c>
     </row>
     <row r="49">
@@ -2578,20 +2578,20 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
+          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>193</v>
+        <v>315</v>
       </c>
       <c r="H49" t="n">
-        <v>24.06181347150259</v>
+        <v>29.49647619047619</v>
       </c>
       <c r="I49" t="n">
-        <v>25.78122408932597</v>
+        <v>30.87753749228234</v>
       </c>
       <c r="J49" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.06687898089171974</v>
       </c>
     </row>
     <row r="50">
@@ -2622,20 +2622,20 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
+          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="H50" t="n">
-        <v>16.24571428571429</v>
+        <v>24.22076923076923</v>
       </c>
       <c r="I50" t="n">
-        <v>18.54288080561994</v>
+        <v>25.95969160458437</v>
       </c>
       <c r="J50" t="n">
-        <v>0.1346153846153846</v>
+        <v>0.06701030927835051</v>
       </c>
     </row>
     <row r="51">
@@ -2666,20 +2666,20 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
+          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="H51" t="n">
-        <v>39.59102564102563</v>
+        <v>16.24571428571429</v>
       </c>
       <c r="I51" t="n">
-        <v>40.99254388112738</v>
+        <v>18.54288080561994</v>
       </c>
       <c r="J51" t="n">
-        <v>0.2077922077922078</v>
+        <v>0.1346153846153846</v>
       </c>
     </row>
     <row r="52">
@@ -2710,20 +2710,20 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="H52" t="n">
-        <v>40.00217391304349</v>
+        <v>39.59102564102563</v>
       </c>
       <c r="I52" t="n">
-        <v>46.29347850587502</v>
+        <v>40.99254388112738</v>
       </c>
       <c r="J52" t="n">
-        <v>0.3111111111111111</v>
+        <v>0.2077922077922078</v>
       </c>
     </row>
     <row r="53">
@@ -2754,19 +2754,63 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>46</v>
+      </c>
+      <c r="H53" t="n">
+        <v>40.00217391304349</v>
+      </c>
+      <c r="I53" t="n">
+        <v>46.29347850587502</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.3111111111111111</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gemini-3-flash-preview</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3.- Analog Depth Gauge_without vernier</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>OPENING_OPENING_V6_10 divisions_per_second</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="G54" t="n">
         <v>34</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H54" t="n">
         <v>20.60882352941176</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I54" t="n">
         <v>21.03269527636045</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J54" t="n">
         <v>0.7575757575757576</v>
       </c>
     </row>
@@ -2813,14 +2857,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.4355</v>
+        <v>16.5072</v>
       </c>
       <c r="C2" t="n">
-        <v>11.9618</v>
+        <v>11.8932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.4355 ± 11.9618</t>
+          <t>16.5072 ± 11.8932</t>
         </is>
       </c>
     </row>
@@ -2831,14 +2875,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.8477</v>
+        <v>17.9106</v>
       </c>
       <c r="C3" t="n">
-        <v>13.0165</v>
+        <v>12.9418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17.8477 ± 13.0165</t>
+          <t>17.9106 ± 12.9418</t>
         </is>
       </c>
     </row>
@@ -2849,14 +2893,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3735</v>
+        <v>0.367</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2734</v>
+        <v>0.2723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.3735 ± 0.2734</t>
+          <t>0.3670 ± 0.2723</t>
         </is>
       </c>
     </row>
@@ -2931,19 +2975,19 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5745</v>
+        <v>2.5787</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1145</v>
+        <v>1.1092</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9036</v>
+        <v>2.9084</v>
       </c>
       <c r="G2" t="n">
         <v>0.0672</v>
       </c>
       <c r="H2" t="n">
-        <v>128.8</v>
+        <v>129.2</v>
       </c>
     </row>
     <row r="3">
@@ -2961,19 +3005,19 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9313</v>
+        <v>2.9494</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7245</v>
+        <v>2.7351</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4278</v>
+        <v>3.4459</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8185</v>
+        <v>0.8168</v>
       </c>
       <c r="H3" t="n">
-        <v>124</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="4">
@@ -2991,19 +3035,19 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9548</v>
+        <v>2.9517</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2467</v>
+        <v>3.2497</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3962</v>
+        <v>3.3935</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4748</v>
+        <v>0.4808</v>
       </c>
       <c r="H4" t="n">
-        <v>132.3</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5">
@@ -3051,19 +3095,19 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>20.13</v>
+        <v>19.8362</v>
       </c>
       <c r="E6" t="n">
-        <v>6.7946</v>
+        <v>7.2353</v>
       </c>
       <c r="F6" t="n">
-        <v>20.3153</v>
+        <v>20.0689</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4823</v>
+        <v>0.463</v>
       </c>
       <c r="H6" t="n">
-        <v>53</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="7">
@@ -3081,19 +3125,19 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>19.3934</v>
+        <v>19.3095</v>
       </c>
       <c r="E7" t="n">
-        <v>6.8231</v>
+        <v>6.9271</v>
       </c>
       <c r="F7" t="n">
-        <v>20.6621</v>
+        <v>20.6085</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4949</v>
+        <v>0.495</v>
       </c>
       <c r="H7" t="n">
-        <v>62.5</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="8">
@@ -3111,19 +3155,19 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>25.9017</v>
+        <v>26.0424</v>
       </c>
       <c r="E8" t="n">
-        <v>8.3855</v>
+        <v>8.368499999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>29.8864</v>
+        <v>30.014</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1529</v>
+        <v>0.1487</v>
       </c>
       <c r="H8" t="n">
-        <v>108.3</v>
+        <v>110.3</v>
       </c>
     </row>
     <row r="9">
@@ -3141,19 +3185,19 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>28.3343</v>
+        <v>28.3608</v>
       </c>
       <c r="E9" t="n">
-        <v>10.3706</v>
+        <v>10.3564</v>
       </c>
       <c r="F9" t="n">
-        <v>30.5867</v>
+        <v>30.6165</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2559</v>
+        <v>0.2575</v>
       </c>
       <c r="H9" t="n">
-        <v>128.5</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="10">
@@ -3168,22 +3212,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>23.0295</v>
+        <v>22.7562</v>
       </c>
       <c r="E10" t="n">
-        <v>8.499700000000001</v>
+        <v>6.4634</v>
       </c>
       <c r="F10" t="n">
-        <v>24.9284</v>
+        <v>24.4275</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2606</v>
+        <v>0.2396</v>
       </c>
       <c r="H10" t="n">
-        <v>124.4</v>
+        <v>138.2</v>
       </c>
     </row>
   </sheetData>
